--- a/artfynd/A 19848-2025 artfynd.xlsx
+++ b/artfynd/A 19848-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7002326</v>
+        <v>7002325</v>
       </c>
       <c r="B2" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422745.2427256278</v>
+        <v>422551</v>
       </c>
       <c r="R2" t="n">
-        <v>6967137.838313367</v>
+        <v>6967171</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7002325</v>
+        <v>7002324</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422550.515011241</v>
+        <v>422555</v>
       </c>
       <c r="R3" t="n">
-        <v>6967171.235725145</v>
+        <v>6967173</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7002324</v>
+        <v>7002326</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422554.6659942334</v>
+        <v>422745</v>
       </c>
       <c r="R4" t="n">
-        <v>6967172.509439431</v>
+        <v>6967138</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
